--- a/PE6201/06_cost_model/PE6201_A2_Cost_Model.xlsx
+++ b/PE6201/06_cost_model/PE6201_A2_Cost_Model.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12460"/>
+    <workbookView windowWidth="29100" windowHeight="13100"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,6 @@
     <sheet name="Break-even" sheetId="11" r:id="rId5"/>
     <sheet name="Cost Levers" sheetId="10" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="238">
   <si>
     <t>Table 1. Cost Model Inputs</t>
   </si>
@@ -307,6 +304,15 @@
     <t>https://openrouter.ai/qwen/qwen3.8-flash</t>
   </si>
   <si>
+    <t>Hy3</t>
+  </si>
+  <si>
+    <t>tencent/hy3</t>
+  </si>
+  <si>
+    <t>https://openrouter.ai/tencent/hy3</t>
+  </si>
+  <si>
     <t>Sequential versus parallel comparison</t>
   </si>
   <si>
@@ -409,10 +415,13 @@
     <t>https://github.com/ziyi-lily/Group-C/blob/main/PE6201/results/D5-qwen3.8-flash_AfterJudge.json</t>
   </si>
   <si>
+    <t>https://github.com/ziyi-lily/Group-C/blob/main/PE6201/05_evaluation/results/d5b_Hy3_AfterJudge.json</t>
+  </si>
+  <si>
     <t>Success measure</t>
   </si>
   <si>
-    <t>The calculation uses code-check passes from 58 trials per model. This measure is available for all four models.</t>
+    <t>The calculation uses code-check passes from 58 trials per model. This measure is available for all five models.</t>
   </si>
   <si>
     <t>Judge results</t>
@@ -721,7 +730,7 @@
     <t>Estimated fallback saving between the lowest and highest D5 pass rates.</t>
   </si>
   <si>
-    <t>Four D5 model files</t>
+    <t>Five D5 model files</t>
   </si>
   <si>
     <t>Overlap</t>
@@ -761,7 +770,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -779,7 +787,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -816,34 +823,34 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -851,15 +858,13 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -867,7 +872,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -875,7 +879,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -883,88 +886,70 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1036,19 +1021,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1060,19 +1045,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1084,19 +1069,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1108,19 +1093,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1132,19 +1117,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1156,19 +1141,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1279,7 +1264,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1368,16 +1353,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1386,120 +1368,123 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1627,6 +1612,15 @@
     <xf numFmtId="180" fontId="2" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1636,7 +1630,22 @@
     <xf numFmtId="179" fontId="2" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1938,157 +1947,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Inputs"/>
-      <sheetName val="Model Results"/>
-      <sheetName val="Viz 1 Monthly Cost"/>
-      <sheetName val="Viz 2 Cost Mix"/>
-      <sheetName val="Viz 3 Sensitivity"/>
-      <sheetName val="Viz 4 Efficiency"/>
-      <sheetName val="Report Draft"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="C5">
-            <v>8000</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>7.6</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="C24">
-            <v>429</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="C28">
-            <v>0.08</v>
-          </cell>
-          <cell r="D28">
-            <v>0.16</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29">
-            <v>1.5</v>
-          </cell>
-          <cell r="D29">
-            <v>7.5</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30">
-            <v>0.15</v>
-          </cell>
-          <cell r="D30">
-            <v>0.6</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="C31">
-            <v>0.15</v>
-          </cell>
-          <cell r="D31">
-            <v>0.47</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Gemma 3 27B</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="E5">
-            <v>0.586206896551724</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>8234.12068965517</v>
-          </cell>
-          <cell r="K5">
-            <v>389.913793103448</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Mistral Medium 3.5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6">
-            <v>0.53448275862069</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>7509.72413793103</v>
-          </cell>
-          <cell r="K6">
-            <v>455.48275862069</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>GPT-4o-mini</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>0.586206896551724</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>7761.20689655172</v>
-          </cell>
-          <cell r="K7">
-            <v>206.844827586207</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Qwen3.8 Flash</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="J8">
-            <v>8619.8275862069</v>
-          </cell>
-          <cell r="K8">
-            <v>1996.93103448276</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -2130,76 +1988,16 @@
         <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -2223,9 +2021,7 @@
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr"/>
@@ -2235,27 +2031,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:gradFill>
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
+                <a:schemeClr val="phClr"/>
               </a:gs>
               <a:gs pos="100000">
                 <a:schemeClr val="phClr"/>
@@ -2264,7 +2056,6 @@
             <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -2307,17 +2098,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -2578,7 +2369,7 @@
       </c>
     </row>
     <row r="14" ht="20.4" spans="1:1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="54" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2730,7 +2521,7 @@
       <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="55">
         <f>SUM(C16:C18)+C21</f>
         <v>429</v>
       </c>
@@ -2745,7 +2536,7 @@
       </c>
     </row>
     <row r="24" ht="20.4" spans="1:1">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="54" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2782,7 +2573,7 @@
       <c r="D26" s="18">
         <v>0.16</v>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="56">
         <v>46284</v>
       </c>
       <c r="F26" s="7" t="s">
@@ -2802,7 +2593,7 @@
       <c r="D27" s="18">
         <v>7.5</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="57">
         <v>46284</v>
       </c>
       <c r="F27" s="9" t="s">
@@ -2822,7 +2613,7 @@
       <c r="D28" s="18">
         <v>0.6</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="57">
         <v>46284</v>
       </c>
       <c r="F28" s="9" t="s">
@@ -2842,41 +2633,61 @@
       <c r="D29" s="18">
         <v>0.47</v>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="58">
         <v>46284</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>89</v>
       </c>
     </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="18">
+        <v>0.0825</v>
+      </c>
+      <c r="D30" s="18">
+        <v>0.33</v>
+      </c>
+      <c r="E30" s="58">
+        <v>46284</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
     <row r="31" ht="20.4" spans="1:1">
-      <c r="A31" s="46" t="s">
-        <v>90</v>
+      <c r="A31" s="54" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B33" s="18">
         <v>33</v>
@@ -2889,15 +2700,15 @@
         <v>0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B34" s="18">
         <v>5</v>
@@ -2913,12 +2724,12 @@
         <v>28</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B35" s="18">
         <v>9</v>
@@ -2934,12 +2745,12 @@
         <v>28</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B36" s="18">
         <v>550849</v>
@@ -2952,15 +2763,15 @@
         <v>-0.38675390170446</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B37" s="18">
         <v>0.0653</v>
@@ -2973,19 +2784,19 @@
         <v>-0.3843797856049</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="5:5">
       <c r="E38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3015,7 +2826,7 @@
   <sheetData>
     <row r="1" ht="28.8" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:17">
@@ -3023,50 +2834,50 @@
         <v>72</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -3106,7 +2917,7 @@
         <f>I3/C3</f>
         <v>389.913793103448</v>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="46">
         <v>0.056806</v>
       </c>
       <c r="M3" s="7">
@@ -3121,7 +2932,7 @@
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -3161,7 +2972,7 @@
         <f>I4/C4</f>
         <v>455.48275862069</v>
       </c>
-      <c r="L4" s="44">
+      <c r="L4" s="47">
         <v>0.054121</v>
       </c>
       <c r="M4" s="9">
@@ -3176,7 +2987,7 @@
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -3216,7 +3027,7 @@
         <f>I5/C5</f>
         <v>206.844827586207</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="47">
         <v>0.049816</v>
       </c>
       <c r="M5" s="9">
@@ -3231,7 +3042,7 @@
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -3271,7 +3082,7 @@
         <f>I6/C6</f>
         <v>1996.93103448276</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="48">
         <v>0.096321</v>
       </c>
       <c r="M6" s="13">
@@ -3286,29 +3097,69 @@
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="C7" s="9">
+        <v>58</v>
+      </c>
+      <c r="D7" s="9">
+        <v>34</v>
+      </c>
+      <c r="E7" s="43">
+        <f>D7/C7</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="F7" s="44">
+        <v>4</v>
+      </c>
+      <c r="G7" s="44">
+        <v>215</v>
+      </c>
+      <c r="H7" s="45">
+        <v>525523</v>
+      </c>
+      <c r="I7" s="49">
+        <v>182935</v>
+      </c>
+      <c r="J7" s="49">
+        <f>H7/C7</f>
+        <v>9060.74137931034</v>
+      </c>
+      <c r="K7" s="49">
+        <f>I7/C7</f>
+        <v>3154.05172413793</v>
+      </c>
+      <c r="L7" s="50">
+        <v>0.12573</v>
+      </c>
+      <c r="M7" s="51">
+        <v>28</v>
+      </c>
+      <c r="N7" s="52">
+        <f>M7/38</f>
+        <v>0.736842105263158</v>
+      </c>
+      <c r="O7" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="53" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="15" t="s">
-        <v>126</v>
+      <c r="A8" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -3318,11 +3169,11 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="15" t="s">
-        <v>128</v>
+      <c r="A9" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -3332,8 +3183,12 @@
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3341,7 +3196,7 @@
       <c r="G10" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3387,7 +3242,7 @@
     </row>
     <row r="2" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2"/>
@@ -3448,55 +3303,55 @@
         <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
@@ -3509,27 +3364,27 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:26">
       <c r="A5" s="9" t="str">
-        <f>'[1]Model Results'!A5</f>
+        <f>'Model Results'!A3</f>
         <v>Gemma 3 27B</v>
       </c>
       <c r="B5" s="9">
-        <f>'[1]Model Results'!E5</f>
+        <f>'Model Results'!E3</f>
         <v>0.586206896551724</v>
       </c>
       <c r="C5" s="9">
-        <f>'[1]Model Results'!J5</f>
+        <f>'Model Results'!J3</f>
         <v>8234.12068965517</v>
       </c>
       <c r="D5" s="9">
-        <f>'[1]Model Results'!K5</f>
+        <f>'Model Results'!K3</f>
         <v>389.913793103448</v>
       </c>
       <c r="E5" s="9">
-        <f>[1]Inputs!C28</f>
+        <f>Inputs!C26</f>
         <v>0.08</v>
       </c>
       <c r="F5" s="9">
-        <f>[1]Inputs!D28</f>
+        <f>Inputs!D26</f>
         <v>0.16</v>
       </c>
       <c r="G5" s="9">
@@ -3541,19 +3396,19 @@
         <v>6.23862068965517e-5</v>
       </c>
       <c r="I5" s="9">
-        <f>[1]Inputs!C9</f>
+        <f>Inputs!C7</f>
         <v>0</v>
       </c>
       <c r="J5" s="9">
         <f>SUM(G5:I5)</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="K5" s="9">
-        <f>(1-B5)*[1]Inputs!C8</f>
+        <f>(1-B5)*Inputs!C6</f>
         <v>3.1448275862069</v>
       </c>
       <c r="L5" s="9">
-        <f>[1]Inputs!C24/[1]Inputs!C5</f>
+        <f>Inputs!C22/Inputs!C3</f>
         <v>0.053625</v>
       </c>
       <c r="M5" s="9">
@@ -3565,15 +3420,15 @@
         <v>0.00123013882352941</v>
       </c>
       <c r="O5" s="9">
-        <f>J5*[1]Inputs!C5</f>
+        <f>J5*Inputs!C3</f>
         <v>5.76892689655172</v>
       </c>
       <c r="P5" s="9">
-        <f>K5*[1]Inputs!C5</f>
+        <f>K5*Inputs!C3</f>
         <v>25158.6206896552</v>
       </c>
       <c r="Q5" s="9">
-        <f>[1]Inputs!C24</f>
+        <f>Inputs!C22</f>
         <v>429</v>
       </c>
       <c r="R5" s="9">
@@ -3591,39 +3446,39 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:26">
       <c r="A6" s="13" t="str">
-        <f>'[1]Model Results'!A6</f>
+        <f>'Model Results'!A4</f>
         <v>Mistral Medium 3.5</v>
       </c>
       <c r="B6" s="13">
-        <f>'[1]Model Results'!E6</f>
+        <f>'Model Results'!E4</f>
         <v>0.53448275862069</v>
       </c>
       <c r="C6" s="13">
-        <f>'[1]Model Results'!J6</f>
+        <f>'Model Results'!J4</f>
         <v>7509.72413793103</v>
       </c>
       <c r="D6" s="13">
-        <f>'[1]Model Results'!K6</f>
+        <f>'Model Results'!K4</f>
         <v>455.48275862069</v>
       </c>
       <c r="E6" s="13">
-        <f>[1]Inputs!C29</f>
+        <f>Inputs!C27</f>
         <v>1.5</v>
       </c>
       <c r="F6" s="13">
-        <f>[1]Inputs!D29</f>
+        <f>Inputs!D27</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="13">
         <f>C6*E6/1000000</f>
-        <v>0.0112645862068965</v>
+        <v>0.0112645862068966</v>
       </c>
       <c r="H6" s="13">
         <f>D6*F6/1000000</f>
         <v>0.00341612068965517</v>
       </c>
       <c r="I6" s="13">
-        <f>[1]Inputs!C9</f>
+        <f>Inputs!C7</f>
         <v>0</v>
       </c>
       <c r="J6" s="13">
@@ -3631,11 +3486,11 @@
         <v>0.0146807068965517</v>
       </c>
       <c r="K6" s="13">
-        <f>(1-B6)*[1]Inputs!C8</f>
+        <f>(1-B6)*Inputs!C6</f>
         <v>3.53793103448276</v>
       </c>
       <c r="L6" s="13">
-        <f>[1]Inputs!C24/[1]Inputs!C5</f>
+        <f>Inputs!C22/Inputs!C3</f>
         <v>0.053625</v>
       </c>
       <c r="M6" s="13">
@@ -3644,18 +3499,18 @@
       </c>
       <c r="N6" s="13">
         <f>J6/B6</f>
-        <v>0.027467129032258</v>
+        <v>0.0274671290322581</v>
       </c>
       <c r="O6" s="13">
-        <f>J6*[1]Inputs!C5</f>
+        <f>J6*Inputs!C3</f>
         <v>117.445655172414</v>
       </c>
       <c r="P6" s="13">
-        <f>K6*[1]Inputs!C5</f>
+        <f>K6*Inputs!C3</f>
         <v>28303.4482758621</v>
       </c>
       <c r="Q6" s="13">
-        <f>[1]Inputs!C24</f>
+        <f>Inputs!C22</f>
         <v>429</v>
       </c>
       <c r="R6" s="13">
@@ -3673,27 +3528,27 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:26">
       <c r="A7" s="9" t="str">
-        <f>'[1]Model Results'!A7</f>
+        <f>'Model Results'!A5</f>
         <v>GPT-4o-mini</v>
       </c>
       <c r="B7" s="9">
-        <f>'[1]Model Results'!E7</f>
+        <f>'Model Results'!E5</f>
         <v>0.586206896551724</v>
       </c>
       <c r="C7" s="9">
-        <f>'[1]Model Results'!J7</f>
+        <f>'Model Results'!J5</f>
         <v>7761.20689655172</v>
       </c>
       <c r="D7" s="9">
-        <f>'[1]Model Results'!K7</f>
+        <f>'Model Results'!K5</f>
         <v>206.844827586207</v>
       </c>
       <c r="E7" s="9">
-        <f>[1]Inputs!C30</f>
+        <f>Inputs!C28</f>
         <v>0.15</v>
       </c>
       <c r="F7" s="9">
-        <f>[1]Inputs!D30</f>
+        <f>Inputs!D28</f>
         <v>0.6</v>
       </c>
       <c r="G7" s="9">
@@ -3705,7 +3560,7 @@
         <v>0.000124106896551724</v>
       </c>
       <c r="I7" s="9">
-        <f>[1]Inputs!C9</f>
+        <f>Inputs!C7</f>
         <v>0</v>
       </c>
       <c r="J7" s="9">
@@ -3713,11 +3568,11 @@
         <v>0.00128828793103448</v>
       </c>
       <c r="K7" s="9">
-        <f>(1-B7)*[1]Inputs!C8</f>
+        <f>(1-B7)*Inputs!C6</f>
         <v>3.1448275862069</v>
       </c>
       <c r="L7" s="9">
-        <f>[1]Inputs!C24/[1]Inputs!C5</f>
+        <f>Inputs!C22/Inputs!C3</f>
         <v>0.053625</v>
       </c>
       <c r="M7" s="9">
@@ -3729,15 +3584,15 @@
         <v>0.00219766764705882</v>
       </c>
       <c r="O7" s="9">
-        <f>J7*[1]Inputs!C5</f>
+        <f>J7*Inputs!C3</f>
         <v>10.3063034482759</v>
       </c>
       <c r="P7" s="9">
-        <f>K7*[1]Inputs!C5</f>
+        <f>K7*Inputs!C3</f>
         <v>25158.6206896552</v>
       </c>
       <c r="Q7" s="9">
-        <f>[1]Inputs!C24</f>
+        <f>Inputs!C22</f>
         <v>429</v>
       </c>
       <c r="R7" s="9">
@@ -3755,39 +3610,39 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:26">
       <c r="A8" s="9" t="str">
-        <f>'[1]Model Results'!A8</f>
+        <f>'Model Results'!A6</f>
         <v>Qwen3.8 Flash</v>
       </c>
       <c r="B8" s="9">
-        <f>'[1]Model Results'!E8</f>
+        <f>'Model Results'!E6</f>
         <v>0.5</v>
       </c>
       <c r="C8" s="9">
-        <f>'[1]Model Results'!J8</f>
+        <f>'Model Results'!J6</f>
         <v>8619.8275862069</v>
       </c>
       <c r="D8" s="9">
-        <f>'[1]Model Results'!K8</f>
+        <f>'Model Results'!K6</f>
         <v>1996.93103448276</v>
       </c>
       <c r="E8" s="9">
-        <f>[1]Inputs!C31</f>
+        <f>Inputs!C29</f>
         <v>0.15</v>
       </c>
       <c r="F8" s="9">
-        <f>[1]Inputs!D31</f>
+        <f>Inputs!D29</f>
         <v>0.47</v>
       </c>
       <c r="G8" s="9">
         <f>C8*E8/1000000</f>
-        <v>0.00129297413793104</v>
+        <v>0.00129297413793103</v>
       </c>
       <c r="H8" s="9">
         <f>D8*F8/1000000</f>
         <v>0.000938557586206897</v>
       </c>
       <c r="I8" s="9">
-        <f>[1]Inputs!C9</f>
+        <f>Inputs!C7</f>
         <v>0</v>
       </c>
       <c r="J8" s="9">
@@ -3795,11 +3650,11 @@
         <v>0.00223153172413793</v>
       </c>
       <c r="K8" s="9">
-        <f>(1-B8)*[1]Inputs!C8</f>
+        <f>(1-B8)*Inputs!C6</f>
         <v>3.8</v>
       </c>
       <c r="L8" s="9">
-        <f>[1]Inputs!C24/[1]Inputs!C5</f>
+        <f>Inputs!C22/Inputs!C3</f>
         <v>0.053625</v>
       </c>
       <c r="M8" s="9">
@@ -3811,15 +3666,15 @@
         <v>0.00446306344827586</v>
       </c>
       <c r="O8" s="9">
-        <f>J8*[1]Inputs!C5</f>
-        <v>17.8522537931035</v>
+        <f>J8*Inputs!C3</f>
+        <v>17.8522537931034</v>
       </c>
       <c r="P8" s="9">
-        <f>K8*[1]Inputs!C5</f>
+        <f>K8*Inputs!C3</f>
         <v>30400</v>
       </c>
       <c r="Q8" s="9">
-        <f>[1]Inputs!C24</f>
+        <f>Inputs!C22</f>
         <v>429</v>
       </c>
       <c r="R8" s="9">
@@ -3836,24 +3691,78 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:26">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
+      <c r="A9" s="9" t="str">
+        <f>'Model Results'!A7</f>
+        <v>Hy3</v>
+      </c>
+      <c r="B9" s="9">
+        <f>'Model Results'!E7</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="C9" s="9">
+        <f>'Model Results'!J7</f>
+        <v>9060.74137931034</v>
+      </c>
+      <c r="D9" s="9">
+        <f>'Model Results'!K7</f>
+        <v>3154.05172413793</v>
+      </c>
+      <c r="E9" s="9">
+        <f>Inputs!C30</f>
+        <v>0.0825</v>
+      </c>
+      <c r="F9" s="9">
+        <f>Inputs!D30</f>
+        <v>0.33</v>
+      </c>
+      <c r="G9" s="9">
+        <f>C9*E9/1000000</f>
+        <v>0.000747511163793103</v>
+      </c>
+      <c r="H9" s="9">
+        <f>D9*F9/1000000</f>
+        <v>0.00104083706896552</v>
+      </c>
+      <c r="I9" s="9">
+        <f>Inputs!C7</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <f>SUM(G9:I9)</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="K9" s="9">
+        <f>(1-B9)*Inputs!C6</f>
+        <v>3.1448275862069</v>
+      </c>
+      <c r="L9" s="9">
+        <f>Inputs!C22/Inputs!C3</f>
+        <v>0.053625</v>
+      </c>
+      <c r="M9" s="9">
+        <f>SUM(J9:L9)</f>
+        <v>3.20024093443965</v>
+      </c>
+      <c r="N9" s="9">
+        <f>J9/B9</f>
+        <v>0.00305071169117647</v>
+      </c>
+      <c r="O9" s="9">
+        <f>J9*Inputs!C3</f>
+        <v>14.306785862069</v>
+      </c>
+      <c r="P9" s="9">
+        <f>K9*Inputs!C3</f>
+        <v>25158.6206896552</v>
+      </c>
+      <c r="Q9" s="9">
+        <f>Inputs!C22</f>
+        <v>429</v>
+      </c>
+      <c r="R9" s="9">
+        <f>SUM(O9:Q9)</f>
+        <v>25601.9274755172</v>
+      </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -3865,10 +3774,10 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:26">
       <c r="A10" s="15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -3897,10 +3806,10 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:26">
       <c r="A11" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -3929,10 +3838,10 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:26">
       <c r="A12" s="15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -5911,7 +5820,7 @@
     </row>
     <row r="2" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5972,31 +5881,31 @@
         <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -6021,7 +5930,7 @@
         <v>Gemma 3 27B</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C5" s="31">
         <v>-0.1</v>
@@ -6031,15 +5940,15 @@
         <v>0.586206896551724</v>
       </c>
       <c r="E5" s="31">
-        <f t="shared" ref="E5:E24" si="0">MAX(0,MIN(1,D5+C5))</f>
+        <f t="shared" ref="E5:E29" si="0">MAX(0,MIN(1,D5+C5))</f>
         <v>0.486206896551724</v>
       </c>
       <c r="F5" s="34">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="G5" s="34">
-        <f>(1-E5)*[1]Inputs!C8</f>
+        <f>(1-E5)*Inputs!C6</f>
         <v>3.9048275862069</v>
       </c>
       <c r="H5" s="34">
@@ -6047,11 +5956,11 @@
         <v>0.053625</v>
       </c>
       <c r="I5" s="34">
-        <f t="shared" ref="I5:I24" si="1">SUM(F5:H5)</f>
-        <v>3.95917370206897</v>
+        <f t="shared" ref="I5:I29" si="1">SUM(F5:H5)</f>
+        <v>3.95917370206896</v>
       </c>
       <c r="J5" s="37">
-        <f>I5*[1]Inputs!C5</f>
+        <f>I5*Inputs!C3</f>
         <v>31673.3896165517</v>
       </c>
       <c r="K5" s="2"/>
@@ -6077,7 +5986,7 @@
         <v>Gemma 3 27B</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C6" s="32">
         <v>-0.05</v>
@@ -6092,10 +6001,10 @@
       </c>
       <c r="F6" s="35">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="G6" s="35">
-        <f>(1-E6)*[1]Inputs!C8</f>
+        <f>(1-E6)*Inputs!C6</f>
         <v>3.5248275862069</v>
       </c>
       <c r="H6" s="35">
@@ -6107,7 +6016,7 @@
         <v>3.57917370206897</v>
       </c>
       <c r="J6" s="38">
-        <f>I6*[1]Inputs!C5</f>
+        <f>I6*Inputs!C3</f>
         <v>28633.3896165517</v>
       </c>
       <c r="K6" s="2"/>
@@ -6133,7 +6042,7 @@
         <v>Gemma 3 27B</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C7" s="32">
         <v>0</v>
@@ -6148,10 +6057,10 @@
       </c>
       <c r="F7" s="35">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="G7" s="35">
-        <f>(1-E7)*[1]Inputs!C8</f>
+        <f>(1-E7)*Inputs!C6</f>
         <v>3.1448275862069</v>
       </c>
       <c r="H7" s="35">
@@ -6163,7 +6072,7 @@
         <v>3.19917370206897</v>
       </c>
       <c r="J7" s="38">
-        <f>I7*[1]Inputs!C5</f>
+        <f>I7*Inputs!C3</f>
         <v>25593.3896165517</v>
       </c>
       <c r="K7" s="2"/>
@@ -6189,7 +6098,7 @@
         <v>Gemma 3 27B</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C8" s="32">
         <v>0.05</v>
@@ -6204,10 +6113,10 @@
       </c>
       <c r="F8" s="35">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="G8" s="35">
-        <f>(1-E8)*[1]Inputs!C8</f>
+        <f>(1-E8)*Inputs!C6</f>
         <v>2.7648275862069</v>
       </c>
       <c r="H8" s="35">
@@ -6216,10 +6125,10 @@
       </c>
       <c r="I8" s="35">
         <f t="shared" si="1"/>
-        <v>2.81917370206897</v>
+        <v>2.81917370206896</v>
       </c>
       <c r="J8" s="38">
-        <f>I8*[1]Inputs!C5</f>
+        <f>I8*Inputs!C3</f>
         <v>22553.3896165517</v>
       </c>
       <c r="K8" s="2"/>
@@ -6245,7 +6154,7 @@
         <v>Gemma 3 27B</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C9" s="32">
         <v>0.1</v>
@@ -6260,10 +6169,10 @@
       </c>
       <c r="F9" s="35">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="G9" s="35">
-        <f>(1-E9)*[1]Inputs!C8</f>
+        <f>(1-E9)*Inputs!C6</f>
         <v>2.3848275862069</v>
       </c>
       <c r="H9" s="35">
@@ -6275,7 +6184,7 @@
         <v>2.43917370206897</v>
       </c>
       <c r="J9" s="38">
-        <f>I9*[1]Inputs!C5</f>
+        <f>I9*Inputs!C3</f>
         <v>19513.3896165517</v>
       </c>
       <c r="K9" s="2"/>
@@ -6301,7 +6210,7 @@
         <v>Mistral Medium 3.5</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C10" s="32">
         <v>-0.1</v>
@@ -6319,7 +6228,7 @@
         <v>0.0146807068965517</v>
       </c>
       <c r="G10" s="35">
-        <f>(1-E10)*[1]Inputs!C8</f>
+        <f>(1-E10)*Inputs!C6</f>
         <v>4.29793103448276</v>
       </c>
       <c r="H10" s="35">
@@ -6331,7 +6240,7 @@
         <v>4.36623674137931</v>
       </c>
       <c r="J10" s="38">
-        <f>I10*[1]Inputs!C5</f>
+        <f>I10*Inputs!C3</f>
         <v>34929.8939310345</v>
       </c>
       <c r="K10" s="2"/>
@@ -6357,7 +6266,7 @@
         <v>Mistral Medium 3.5</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C11" s="32">
         <v>-0.05</v>
@@ -6375,7 +6284,7 @@
         <v>0.0146807068965517</v>
       </c>
       <c r="G11" s="35">
-        <f>(1-E11)*[1]Inputs!C8</f>
+        <f>(1-E11)*Inputs!C6</f>
         <v>3.91793103448276</v>
       </c>
       <c r="H11" s="35">
@@ -6387,7 +6296,7 @@
         <v>3.98623674137931</v>
       </c>
       <c r="J11" s="38">
-        <f>I11*[1]Inputs!C5</f>
+        <f>I11*Inputs!C3</f>
         <v>31889.8939310345</v>
       </c>
       <c r="K11" s="2"/>
@@ -6413,7 +6322,7 @@
         <v>Mistral Medium 3.5</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C12" s="32">
         <v>0</v>
@@ -6431,7 +6340,7 @@
         <v>0.0146807068965517</v>
       </c>
       <c r="G12" s="35">
-        <f>(1-E12)*[1]Inputs!C8</f>
+        <f>(1-E12)*Inputs!C6</f>
         <v>3.53793103448276</v>
       </c>
       <c r="H12" s="35">
@@ -6443,7 +6352,7 @@
         <v>3.60623674137931</v>
       </c>
       <c r="J12" s="38">
-        <f>I12*[1]Inputs!C5</f>
+        <f>I12*Inputs!C3</f>
         <v>28849.8939310345</v>
       </c>
       <c r="K12" s="2"/>
@@ -6469,7 +6378,7 @@
         <v>Mistral Medium 3.5</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C13" s="32">
         <v>0.05</v>
@@ -6487,7 +6396,7 @@
         <v>0.0146807068965517</v>
       </c>
       <c r="G13" s="35">
-        <f>(1-E13)*[1]Inputs!C8</f>
+        <f>(1-E13)*Inputs!C6</f>
         <v>3.15793103448276</v>
       </c>
       <c r="H13" s="35">
@@ -6499,7 +6408,7 @@
         <v>3.22623674137931</v>
       </c>
       <c r="J13" s="38">
-        <f>I13*[1]Inputs!C5</f>
+        <f>I13*Inputs!C3</f>
         <v>25809.8939310345</v>
       </c>
       <c r="K13" s="2"/>
@@ -6525,7 +6434,7 @@
         <v>Mistral Medium 3.5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C14" s="32">
         <v>0.1</v>
@@ -6543,7 +6452,7 @@
         <v>0.0146807068965517</v>
       </c>
       <c r="G14" s="35">
-        <f>(1-E14)*[1]Inputs!C8</f>
+        <f>(1-E14)*Inputs!C6</f>
         <v>2.77793103448276</v>
       </c>
       <c r="H14" s="35">
@@ -6555,7 +6464,7 @@
         <v>2.84623674137931</v>
       </c>
       <c r="J14" s="38">
-        <f>I14*[1]Inputs!C5</f>
+        <f>I14*Inputs!C3</f>
         <v>22769.8939310345</v>
       </c>
       <c r="K14" s="2"/>
@@ -6581,7 +6490,7 @@
         <v>GPT-4o-mini</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C15" s="32">
         <v>-0.1</v>
@@ -6599,7 +6508,7 @@
         <v>0.00128828793103448</v>
       </c>
       <c r="G15" s="35">
-        <f>(1-E15)*[1]Inputs!C8</f>
+        <f>(1-E15)*Inputs!C6</f>
         <v>3.9048275862069</v>
       </c>
       <c r="H15" s="35">
@@ -6611,8 +6520,8 @@
         <v>3.95974087413793</v>
       </c>
       <c r="J15" s="38">
-        <f>I15*[1]Inputs!C5</f>
-        <v>31677.9269931035</v>
+        <f>I15*Inputs!C3</f>
+        <v>31677.9269931034</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -6637,7 +6546,7 @@
         <v>GPT-4o-mini</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C16" s="32">
         <v>-0.05</v>
@@ -6655,7 +6564,7 @@
         <v>0.00128828793103448</v>
       </c>
       <c r="G16" s="35">
-        <f>(1-E16)*[1]Inputs!C8</f>
+        <f>(1-E16)*Inputs!C6</f>
         <v>3.5248275862069</v>
       </c>
       <c r="H16" s="35">
@@ -6667,8 +6576,8 @@
         <v>3.57974087413793</v>
       </c>
       <c r="J16" s="38">
-        <f>I16*[1]Inputs!C5</f>
-        <v>28637.9269931035</v>
+        <f>I16*Inputs!C3</f>
+        <v>28637.9269931034</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -6693,7 +6602,7 @@
         <v>GPT-4o-mini</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C17" s="32">
         <v>0</v>
@@ -6711,7 +6620,7 @@
         <v>0.00128828793103448</v>
       </c>
       <c r="G17" s="35">
-        <f>(1-E17)*[1]Inputs!C8</f>
+        <f>(1-E17)*Inputs!C6</f>
         <v>3.1448275862069</v>
       </c>
       <c r="H17" s="35">
@@ -6723,8 +6632,8 @@
         <v>3.19974087413793</v>
       </c>
       <c r="J17" s="38">
-        <f>I17*[1]Inputs!C5</f>
-        <v>25597.9269931035</v>
+        <f>I17*Inputs!C3</f>
+        <v>25597.9269931034</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -6749,7 +6658,7 @@
         <v>GPT-4o-mini</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C18" s="32">
         <v>0.05</v>
@@ -6767,7 +6676,7 @@
         <v>0.00128828793103448</v>
       </c>
       <c r="G18" s="35">
-        <f>(1-E18)*[1]Inputs!C8</f>
+        <f>(1-E18)*Inputs!C6</f>
         <v>2.7648275862069</v>
       </c>
       <c r="H18" s="35">
@@ -6779,8 +6688,8 @@
         <v>2.81974087413793</v>
       </c>
       <c r="J18" s="38">
-        <f>I18*[1]Inputs!C5</f>
-        <v>22557.9269931035</v>
+        <f>I18*Inputs!C3</f>
+        <v>22557.9269931034</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -6805,7 +6714,7 @@
         <v>GPT-4o-mini</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C19" s="32">
         <v>0.1</v>
@@ -6823,7 +6732,7 @@
         <v>0.00128828793103448</v>
       </c>
       <c r="G19" s="35">
-        <f>(1-E19)*[1]Inputs!C8</f>
+        <f>(1-E19)*Inputs!C6</f>
         <v>2.3848275862069</v>
       </c>
       <c r="H19" s="35">
@@ -6835,8 +6744,8 @@
         <v>2.43974087413793</v>
       </c>
       <c r="J19" s="38">
-        <f>I19*[1]Inputs!C5</f>
-        <v>19517.9269931035</v>
+        <f>I19*Inputs!C3</f>
+        <v>19517.9269931034</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -6861,7 +6770,7 @@
         <v>Qwen3.8 Flash</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C20" s="32">
         <v>-0.1</v>
@@ -6879,7 +6788,7 @@
         <v>0.00223153172413793</v>
       </c>
       <c r="G20" s="35">
-        <f>(1-E20)*[1]Inputs!C8</f>
+        <f>(1-E20)*Inputs!C6</f>
         <v>4.56</v>
       </c>
       <c r="H20" s="35">
@@ -6891,7 +6800,7 @@
         <v>4.61585653172414</v>
       </c>
       <c r="J20" s="38">
-        <f>I20*[1]Inputs!C5</f>
+        <f>I20*Inputs!C3</f>
         <v>36926.8522537931</v>
       </c>
       <c r="K20" s="2"/>
@@ -6917,7 +6826,7 @@
         <v>Qwen3.8 Flash</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C21" s="32">
         <v>-0.05</v>
@@ -6935,7 +6844,7 @@
         <v>0.00223153172413793</v>
       </c>
       <c r="G21" s="35">
-        <f>(1-E21)*[1]Inputs!C8</f>
+        <f>(1-E21)*Inputs!C6</f>
         <v>4.18</v>
       </c>
       <c r="H21" s="35">
@@ -6947,7 +6856,7 @@
         <v>4.23585653172414</v>
       </c>
       <c r="J21" s="38">
-        <f>I21*[1]Inputs!C5</f>
+        <f>I21*Inputs!C3</f>
         <v>33886.8522537931</v>
       </c>
       <c r="K21" s="2"/>
@@ -6973,7 +6882,7 @@
         <v>Qwen3.8 Flash</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C22" s="32">
         <v>0</v>
@@ -6991,7 +6900,7 @@
         <v>0.00223153172413793</v>
       </c>
       <c r="G22" s="35">
-        <f>(1-E22)*[1]Inputs!C8</f>
+        <f>(1-E22)*Inputs!C6</f>
         <v>3.8</v>
       </c>
       <c r="H22" s="35">
@@ -7003,7 +6912,7 @@
         <v>3.85585653172414</v>
       </c>
       <c r="J22" s="38">
-        <f>I22*[1]Inputs!C5</f>
+        <f>I22*Inputs!C3</f>
         <v>30846.8522537931</v>
       </c>
       <c r="K22" s="2"/>
@@ -7029,7 +6938,7 @@
         <v>Qwen3.8 Flash</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C23" s="32">
         <v>0.05</v>
@@ -7047,7 +6956,7 @@
         <v>0.00223153172413793</v>
       </c>
       <c r="G23" s="35">
-        <f>(1-E23)*[1]Inputs!C8</f>
+        <f>(1-E23)*Inputs!C6</f>
         <v>3.42</v>
       </c>
       <c r="H23" s="35">
@@ -7059,7 +6968,7 @@
         <v>3.47585653172414</v>
       </c>
       <c r="J23" s="38">
-        <f>I23*[1]Inputs!C5</f>
+        <f>I23*Inputs!C3</f>
         <v>27806.8522537931</v>
       </c>
       <c r="K23" s="2"/>
@@ -7085,12 +6994,12 @@
         <v>Qwen3.8 Flash</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C24" s="33">
         <v>0.1</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <f>'Cost Model'!B8</f>
         <v>0.5</v>
       </c>
@@ -7103,7 +7012,7 @@
         <v>0.00223153172413793</v>
       </c>
       <c r="G24" s="36">
-        <f>(1-E24)*[1]Inputs!C8</f>
+        <f>(1-E24)*Inputs!C6</f>
         <v>3.04</v>
       </c>
       <c r="H24" s="36">
@@ -7115,7 +7024,7 @@
         <v>3.09585653172414</v>
       </c>
       <c r="J24" s="39">
-        <f>I24*[1]Inputs!C5</f>
+        <f>I24*Inputs!C3</f>
         <v>24766.8522537931</v>
       </c>
       <c r="K24" s="2"/>
@@ -7136,18 +7045,46 @@
       <c r="Z24" s="2"/>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:26">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="A25" s="9" t="str">
+        <f>'Cost Model'!A9</f>
+        <v>Hy3</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" s="32">
+        <v>-0.1</v>
+      </c>
+      <c r="D25" s="32">
+        <f>'Cost Model'!B9</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="E25" s="32">
+        <f t="shared" si="0"/>
+        <v>0.486206896551724</v>
+      </c>
+      <c r="F25" s="35">
+        <f>'Cost Model'!J9</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="G25" s="35">
+        <f>(1-E25)*Inputs!C6</f>
+        <v>3.9048275862069</v>
+      </c>
+      <c r="H25" s="35">
+        <f>'Cost Model'!L9</f>
+        <v>0.053625</v>
+      </c>
+      <c r="I25" s="35">
+        <f t="shared" si="1"/>
+        <v>3.96024093443965</v>
+      </c>
+      <c r="J25" s="35">
+        <f>I25*Inputs!C3</f>
+        <v>31681.9274755172</v>
+      </c>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -7164,22 +7101,46 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:26">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="9" t="str">
+        <f>'Cost Model'!A9</f>
+        <v>Hy3</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="C26" s="32">
+        <v>-0.05</v>
+      </c>
+      <c r="D26" s="32">
+        <f>'Cost Model'!B9</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="E26" s="32">
+        <f t="shared" si="0"/>
+        <v>0.536206896551724</v>
+      </c>
+      <c r="F26" s="35">
+        <f>'Cost Model'!J9</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="G26" s="35">
+        <f>(1-E26)*Inputs!C6</f>
+        <v>3.5248275862069</v>
+      </c>
+      <c r="H26" s="35">
+        <f>'Cost Model'!L9</f>
+        <v>0.053625</v>
+      </c>
+      <c r="I26" s="35">
+        <f t="shared" si="1"/>
+        <v>3.58024093443966</v>
+      </c>
+      <c r="J26" s="35">
+        <f>I26*Inputs!C3</f>
+        <v>28641.9274755172</v>
+      </c>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -7196,22 +7157,46 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:26">
-      <c r="A27" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="A27" s="9" t="str">
+        <f>'Cost Model'!A9</f>
+        <v>Hy3</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="32">
+        <v>0</v>
+      </c>
+      <c r="D27" s="32">
+        <f>'Cost Model'!B9</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="E27" s="32">
+        <f t="shared" si="0"/>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="F27" s="35">
+        <f>'Cost Model'!J9</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="G27" s="35">
+        <f>(1-E27)*Inputs!C6</f>
+        <v>3.1448275862069</v>
+      </c>
+      <c r="H27" s="35">
+        <f>'Cost Model'!L9</f>
+        <v>0.053625</v>
+      </c>
+      <c r="I27" s="35">
+        <f t="shared" si="1"/>
+        <v>3.20024093443965</v>
+      </c>
+      <c r="J27" s="35">
+        <f>I27*Inputs!C3</f>
+        <v>25601.9274755172</v>
+      </c>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -7228,22 +7213,46 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:26">
-      <c r="A28" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="A28" s="9" t="str">
+        <f>'Cost Model'!A9</f>
+        <v>Hy3</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="32">
+        <v>0.05</v>
+      </c>
+      <c r="D28" s="32">
+        <f>'Cost Model'!B9</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="E28" s="32">
+        <f t="shared" si="0"/>
+        <v>0.636206896551724</v>
+      </c>
+      <c r="F28" s="35">
+        <f>'Cost Model'!J9</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="G28" s="35">
+        <f>(1-E28)*Inputs!C6</f>
+        <v>2.7648275862069</v>
+      </c>
+      <c r="H28" s="35">
+        <f>'Cost Model'!L9</f>
+        <v>0.053625</v>
+      </c>
+      <c r="I28" s="35">
+        <f t="shared" si="1"/>
+        <v>2.82024093443965</v>
+      </c>
+      <c r="J28" s="35">
+        <f>I28*Inputs!C3</f>
+        <v>22561.9274755172</v>
+      </c>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -7260,18 +7269,46 @@
       <c r="Z28" s="2"/>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:26">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
+      <c r="A29" s="9" t="str">
+        <f>'Cost Model'!A9</f>
+        <v>Hy3</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="32">
+        <f>'Cost Model'!B9</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="E29" s="32">
+        <f t="shared" si="0"/>
+        <v>0.686206896551724</v>
+      </c>
+      <c r="F29" s="35">
+        <f>'Cost Model'!J9</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="G29" s="35">
+        <f>(1-E29)*Inputs!C6</f>
+        <v>2.3848275862069</v>
+      </c>
+      <c r="H29" s="35">
+        <f>'Cost Model'!L9</f>
+        <v>0.053625</v>
+      </c>
+      <c r="I29" s="35">
+        <f t="shared" si="1"/>
+        <v>2.44024093443966</v>
+      </c>
+      <c r="J29" s="35">
+        <f>I29*Inputs!C3</f>
+        <v>19521.9274755172</v>
+      </c>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -7316,8 +7353,12 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:26">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -7344,8 +7385,12 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:26">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -7372,8 +7417,12 @@
       <c r="Z32" s="2"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:26">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -8763,7 +8812,7 @@
     </row>
     <row r="2" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8793,37 +8842,37 @@
     </row>
     <row r="3" ht="21" customHeight="1" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L3" s="30"/>
       <c r="M3" s="2"/>
@@ -8852,7 +8901,7 @@
       </c>
       <c r="C4" s="24">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="D4" s="24">
         <f>'Cost Model'!J6</f>
@@ -8863,7 +8912,7 @@
         <v>0.0139595910344828</v>
       </c>
       <c r="F4" s="24">
-        <f>[1]Inputs!C8</f>
+        <f>Inputs!C6</f>
         <v>7.6</v>
       </c>
       <c r="G4" s="27">
@@ -8884,7 +8933,7 @@
       </c>
       <c r="K4" s="27">
         <f>J4-I4</f>
-        <v>-0.051724137931034</v>
+        <v>-0.0517241379310345</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="2"/>
@@ -8913,7 +8962,7 @@
       </c>
       <c r="C5" s="25">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="D5" s="25">
         <f>'Cost Model'!J7</f>
@@ -8924,12 +8973,12 @@
         <v>0.000567172068965517</v>
       </c>
       <c r="F5" s="25">
-        <f>[1]Inputs!C8</f>
+        <f>Inputs!C6</f>
         <v>7.6</v>
       </c>
       <c r="G5" s="28">
         <f>E5/F5</f>
-        <v>7.46279038112522e-5</v>
+        <v>7.46279038112523e-5</v>
       </c>
       <c r="H5" s="28">
         <f>1-G5</f>
@@ -8974,7 +9023,7 @@
       </c>
       <c r="C6" s="26">
         <f>'Cost Model'!J5</f>
-        <v>0.000721115862068965</v>
+        <v>0.000721115862068966</v>
       </c>
       <c r="D6" s="26">
         <f>'Cost Model'!J8</f>
@@ -8985,7 +9034,7 @@
         <v>0.00151041586206897</v>
       </c>
       <c r="F6" s="26">
-        <f>[1]Inputs!C8</f>
+        <f>Inputs!C6</f>
         <v>7.6</v>
       </c>
       <c r="G6" s="29">
@@ -9006,7 +9055,7 @@
       </c>
       <c r="K6" s="29">
         <f>J6-I6</f>
-        <v>-0.086206896551724</v>
+        <v>-0.0862068965517241</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="2"/>
@@ -9025,17 +9074,50 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:26">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="A7" s="24" t="str">
+        <f>'Cost Model'!A5</f>
+        <v>Gemma 3 27B</v>
+      </c>
+      <c r="B7" s="24" t="str">
+        <f>'Cost Model'!A9</f>
+        <v>Hy3</v>
+      </c>
+      <c r="C7" s="24">
+        <f>'Cost Model'!J5</f>
+        <v>0.000721115862068966</v>
+      </c>
+      <c r="D7" s="24">
+        <f>'Cost Model'!J9</f>
+        <v>0.00178834823275862</v>
+      </c>
+      <c r="E7" s="24">
+        <f>D7-C7</f>
+        <v>0.00106723237068966</v>
+      </c>
+      <c r="F7" s="24">
+        <f>Inputs!C6</f>
+        <v>7.6</v>
+      </c>
+      <c r="G7" s="24">
+        <f>E7/F7</f>
+        <v>0.000140425311932849</v>
+      </c>
+      <c r="H7" s="24">
+        <f>1-G7</f>
+        <v>0.999859574688067</v>
+      </c>
+      <c r="I7" s="24">
+        <f>'Cost Model'!B5</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="J7" s="24">
+        <f>'Cost Model'!B9</f>
+        <v>0.586206896551724</v>
+      </c>
+      <c r="K7" s="24">
+        <f>J7-I7</f>
+        <v>0</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -9054,10 +9136,10 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:26">
       <c r="A8" s="15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -9086,10 +9168,10 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:26">
       <c r="A9" s="15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -9118,10 +9200,10 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:26">
       <c r="A10" s="15" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -11137,7 +11219,7 @@
     </row>
     <row r="2" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11195,38 +11277,38 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:26">
       <c r="A4" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="21" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -11245,10 +11327,10 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:26">
       <c r="A5" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C5" s="8">
         <v>2981</v>
@@ -11265,20 +11347,20 @@
         <v>0.0513250587051325</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="22" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -11297,10 +11379,10 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:26">
       <c r="A6" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C6" s="10">
         <v>5</v>
@@ -11320,17 +11402,17 @@
         <v>28</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="22" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -11349,10 +11431,10 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:26">
       <c r="A7" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C7" s="10">
         <v>550849</v>
@@ -11369,20 +11451,20 @@
         <v>-0.38675390170446</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -11401,10 +11483,10 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:26">
       <c r="A8" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C8" s="11">
         <v>0.0653</v>
@@ -11421,17 +11503,17 @@
         <v>-0.3843797856049</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H8" s="18">
-        <f>-(D8-C8)/33*[1]Inputs!C5</f>
+        <f>-(D8-C8)/33*Inputs!C3</f>
         <v>6.08484848484848</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -11452,10 +11534,10 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:26">
       <c r="A9" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C9" s="10">
         <v>41.86</v>
@@ -11472,16 +11554,16 @@
         <v>0.450310559006211</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -11502,10 +11584,10 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:26">
       <c r="A10" s="9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C10" s="12">
         <v>0.0862068965517241</v>
@@ -11522,17 +11604,17 @@
         <v>0.400000000000003</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H10" s="18">
-        <f>(D10-C10)*[1]Inputs!C8*[1]Inputs!C5</f>
+        <f>(D10-C10)*Inputs!C6*Inputs!C3</f>
         <v>2096.55172413795</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -11553,10 +11635,10 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:26">
       <c r="A11" s="13" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C11" s="14">
         <v>0.5</v>
@@ -11573,17 +11655,17 @@
         <v>0.172413793103448</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H11" s="19">
-        <f>(D11-C11)*[1]Inputs!C8*[1]Inputs!C5</f>
+        <f>(D11-C11)*Inputs!C6*Inputs!C3</f>
         <v>5241.37931034482</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -11632,10 +11714,10 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:26">
       <c r="A13" s="15" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -11664,10 +11746,10 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:26">
       <c r="A14" s="15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -11696,10 +11778,10 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:26">
       <c r="A15" s="15" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
